--- a/artfynd/A 39135-2022 artfynd.xlsx
+++ b/artfynd/A 39135-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39135-2022 artfynd.xlsx
+++ b/artfynd/A 39135-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1254,121 +1254,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>65964392</v>
-      </c>
-      <c r="B7" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Nottjärn, öster om, Dlr</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>563878.4680272879</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6725081.108025571</v>
-      </c>
-      <c r="S7" t="n">
-        <v>100</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Falun</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Svärdsjö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2017-05-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2017-05-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Urban Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Urban Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39135-2022 artfynd.xlsx
+++ b/artfynd/A 39135-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1254,6 +1254,121 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>65964392</v>
+      </c>
+      <c r="B7" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nottjärn, öster om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563878.4680272879</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6725081.108025571</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärdsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-05-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-05-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Urban Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
